--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,77 +438,77 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.195223077171645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.270993666513398</v>
+        <v>-3.699864475570126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.627674619468722</v>
+        <v>10.91267204907505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-6.605218288253476</v>
+        <v>3.605836094432029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-6.229457872509628</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-1.528824231867586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.899616609252132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -518,100 +518,10 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.195223077171645</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>10.91267204907505</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-3.699864475570126</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.605836094432029</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-6.229457872509628</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-1.528824231867586</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.899616609252132</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
         <v>-2.760497454554507</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,90 +425,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
+          <t>dif_mean_last_120_matches_red_cards</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.195223077171645</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.699864475570126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.91267204907505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.605836094432029</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lxyu7Met</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.229457872509628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.528824231867586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.899616609252132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -518,11 +518,21 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.760497454554507</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,104 +434,191 @@
           <t>dif_mean_last_120_matches_red_cards</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1858363880754785</v>
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.012971111189509</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1858363880754785</v>
+        <v>0.4615479624468221</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0.1858363880754785</v>
+      </c>
+      <c r="C10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1858363880754785</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,200 +425,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_start</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>AsQgyP6l</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-1.271453986565998</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.012971111189509</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4615479624468221</v>
+        <v>-0.7983458157174819</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1.508056517169033</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0.7392072943614173</v>
       </c>
       <c r="C7" t="n">
+        <v>1.433864764832862</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.3844246114038081</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.857532782252324</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1858363880754785</v>
+        <v>1.153225389032646</v>
       </c>
       <c r="C10" t="n">
+        <v>-1.32504284681168</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.6209786968280659</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1.034948346320517</v>
       </c>
       <c r="C12" t="n">
+        <v>-6.568945973140764</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1858363880754785</v>
+        <v>0.8279635215742916</v>
       </c>
       <c r="C13" t="n">
+        <v>-8.828314703914325</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.4139454269030626</v>
       </c>
       <c r="C14" t="n">
+        <v>1.440019918210428</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.8574843370735463</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>S2WzL3M7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.217718773441807</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OAZJOoNr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.7687765550394495</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WzwSMPie</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.3252376448689658</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-2.572501456399416</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,21 +439,6 @@
           <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -467,79 +452,43 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>vNHAXt6D</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>h2acepbK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0.7983458157174819</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>KdJMr7EE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7983458157174819</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -555,15 +504,6 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -577,15 +517,6 @@
       <c r="C7" t="n">
         <v>1.433864764832862</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -599,15 +530,6 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -621,15 +543,6 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -643,15 +556,6 @@
       <c r="C10" t="n">
         <v>-1.32504284681168</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -665,36 +569,18 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.034948346320517</v>
+        <v>-0.4139454269030626</v>
       </c>
       <c r="C12" t="n">
-        <v>-6.568945973140764</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
+        <v>1.440019918210428</v>
       </c>
     </row>
     <row r="13">
@@ -709,36 +595,18 @@
       <c r="C13" t="n">
         <v>-8.828314703914325</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4139454269030626</v>
+        <v>1.034948346320517</v>
       </c>
       <c r="C14" t="n">
-        <v>1.440019918210428</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>-6.568945973140764</v>
       </c>
     </row>
     <row r="15">
@@ -753,15 +621,6 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -775,15 +634,6 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -797,15 +647,6 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -819,15 +660,6 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -839,15 +671,6 @@
         <v>-2.572501456399416</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,253 +425,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
+          <t>dif_mean_last_120_matches_red_cards</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.271453986565998</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7983458157174819</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+        <v>1.84010583430354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.508056517169033</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.7392072943614173</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.433864764832862</v>
+        <v>0.1858363880754785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3844246114038081</v>
-      </c>
-      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.857532782252324</v>
-      </c>
-      <c r="C9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.153225389032646</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.32504284681168</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.6209786968280659</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.4139454269030626</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.440019918210428</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.8279635215742916</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-8.828314703914325</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.034948346320517</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-6.568945973140764</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.8574843370735463</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>S2WzL3M7</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.217718773441807</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OAZJOoNr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.7687765550394495</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WzwSMPie</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.3252376448689658</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>vwbmU7aL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-2.572501456399416</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
+        <v>-0.08987518629586511</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,13 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_red_cards</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
     </row>
@@ -442,7 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1858363880754785</v>
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -454,6 +462,9 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -462,7 +473,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.84010583430354</v>
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +486,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1858363880754785</v>
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -482,7 +499,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1858363880754785</v>
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +512,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1858363880754785</v>
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -504,6 +527,9 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -512,7 +538,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0.3664281570914146</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8980734948674671</v>
       </c>
     </row>
     <row r="10">
@@ -522,7 +551,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08987518629586511</v>
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
